--- a/ESP32/NFC_Card_Payment_System/production/bom/NFC_Card_Payment_System_BOM.xlsx
+++ b/ESP32/NFC_Card_Payment_System/production/bom/NFC_Card_Payment_System_BOM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PFG-ELECTRICAL-ENGR\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PFG-ELECTRICAL-ENGR\Documents\Galaxies\Resources\Personal Stuffs\Kicad Design\Projects\ESP32\NFC_Card_Payment_System\production\bom\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ECAE625-D57A-4826-A824-A11348A40D3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D1BACD9-0514-44D3-BE22-6F0261EAC15D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{78F08B1A-A6D5-4604-8FC6-7508424A5F87}"/>
+    <workbookView xWindow="1080" yWindow="1080" windowWidth="21600" windowHeight="11295" xr2:uid="{78F08B1A-A6D5-4604-8FC6-7508424A5F87}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1291,7 +1291,7 @@
       </c>
       <c r="F31" s="5"/>
       <c r="G31" s="5">
-        <v>12000</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -1310,7 +1310,7 @@
       <c r="F33" s="7"/>
       <c r="G33" s="5">
         <f>SUM(G2:G32)</f>
-        <v>154600</v>
+        <v>160600</v>
       </c>
     </row>
   </sheetData>
